--- a/checklists/excel/architect/architecture.xlsx
+++ b/checklists/excel/architect/architecture.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Architecture" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Architecture Principles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,94 +425,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item Text</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Main Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to Measure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>System design aligns with enterprise architecture (MUST)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Architecture Principles</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enterprise patterns followed; Technology stack approved; Integration standards met</t>
+          <t>Verify enterprise architecture compliance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implementation should align with enterprise architecture principles</t>
+          <t>Ensure the implementation follows enterprise architecture principles and standards.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Follows enterprise patterns and technology stack guidelines</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Architecture review and compliance check</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Long-term technical strategy considered (GOOD)</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Architecture Principles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology evolution planned; Technical debt managed; Future scalability ensured</t>
+          <t>Check cross-cutting concerns</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Design should support long-term technical objectives</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cross-cutting concerns properly addressed (MUST)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Security, logging, monitoring, caching implemented consistently; Standards compliance verified</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>All cross-cutting concerns should be consistently implemented</t>
+          <t>Verify that cross-cutting concerns like security, logging, and monitoring are consistently implemented.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aspect-oriented programming or consistent implementation patterns</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Code review and static analysis</t>
         </is>
       </c>
     </row>
